--- a/Cambiar Lotes/__ListaMetodos.xlsx
+++ b/Cambiar Lotes/__ListaMetodos.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Hoja1!$A$1:$C$637</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Hoja1!$A$1:$C$638</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1911" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1914" uniqueCount="633">
   <si>
     <t xml:space="preserve">Metodo</t>
   </si>
@@ -34,15 +34,21 @@
     <t xml:space="preserve">CentroServicio</t>
   </si>
   <si>
+    <t xml:space="preserve">ICPOES-Metales-P-Sólidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fósforo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hidrolab SCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">ICPMS-Metales-NCh409</t>
   </si>
   <si>
     <t xml:space="preserve">Cinc</t>
   </si>
   <si>
-    <t xml:space="preserve">Hidrolab SCL</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cobre</t>
   </si>
   <si>
@@ -986,9 +992,6 @@
   </si>
   <si>
     <t xml:space="preserve">EAM-P-Cloruroestanoso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fósforo</t>
   </si>
   <si>
     <t xml:space="preserve">EAM-P-Cloruroestanoso-RB</t>
@@ -2217,7 +2220,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C637"/>
+  <dimension ref="A1:C638"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.57"/>
@@ -2249,10 +2252,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>5</v>
@@ -2260,10 +2263,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>5</v>
@@ -2271,10 +2274,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
@@ -2282,10 +2285,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>5</v>
@@ -2293,10 +2296,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>5</v>
@@ -2304,10 +2307,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -2315,10 +2318,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -2326,10 +2329,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>5</v>
@@ -2337,10 +2340,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -2348,29 +2351,29 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="A13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -2381,10 +2384,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -2392,10 +2395,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -2403,7 +2406,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>20</v>
@@ -2425,10 +2428,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -2436,7 +2439,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>25</v>
@@ -2447,10 +2450,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -2458,10 +2461,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -2469,7 +2472,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>29</v>
@@ -2483,7 +2486,7 @@
         <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -2491,10 +2494,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -2505,7 +2508,7 @@
         <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -2513,10 +2516,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -2524,10 +2527,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -2535,10 +2538,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -2546,10 +2549,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -2557,10 +2560,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
@@ -2568,10 +2571,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>5</v>
@@ -2579,10 +2582,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>5</v>
@@ -2590,10 +2593,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>5</v>
@@ -2601,10 +2604,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>5</v>
@@ -2612,10 +2615,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
@@ -2736,7 +2739,7 @@
         <v>65</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>5</v>
@@ -2744,10 +2747,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>5</v>
@@ -2755,10 +2758,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>5</v>
@@ -2766,10 +2769,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>5</v>
@@ -2777,10 +2780,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>5</v>
@@ -2788,10 +2791,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>5</v>
@@ -2802,7 +2805,7 @@
         <v>72</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>5</v>
@@ -2810,10 +2813,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
@@ -2835,7 +2838,7 @@
         <v>77</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>5</v>
@@ -2843,10 +2846,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>5</v>
@@ -2854,10 +2857,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>5</v>
@@ -2865,10 +2868,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>5</v>
@@ -2879,7 +2882,7 @@
         <v>82</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>5</v>
@@ -2887,7 +2890,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>83</v>
@@ -2901,7 +2904,7 @@
         <v>65</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>5</v>
@@ -2909,10 +2912,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>5</v>
@@ -2920,10 +2923,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>5</v>
@@ -2934,7 +2937,7 @@
         <v>72</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>5</v>
@@ -2942,10 +2945,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>5</v>
@@ -2953,10 +2956,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>5</v>
@@ -2964,10 +2967,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>5</v>
@@ -2975,10 +2978,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>5</v>
@@ -2986,10 +2989,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>5</v>
@@ -2997,10 +3000,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>5</v>
@@ -3011,7 +3014,7 @@
         <v>65</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>5</v>
@@ -3019,10 +3022,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>5</v>
@@ -3030,10 +3033,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>5</v>
@@ -3041,10 +3044,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>5</v>
@@ -3055,7 +3058,7 @@
         <v>72</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>5</v>
@@ -3063,7 +3066,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>92</v>
@@ -3077,7 +3080,7 @@
         <v>93</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>5</v>
@@ -3085,10 +3088,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>5</v>
@@ -3096,10 +3099,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>5</v>
@@ -3110,7 +3113,7 @@
         <v>65</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>5</v>
@@ -3118,10 +3121,10 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>5</v>
@@ -3129,10 +3132,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>5</v>
@@ -3140,10 +3143,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>5</v>
@@ -3154,7 +3157,7 @@
         <v>72</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>5</v>
@@ -3162,10 +3165,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>5</v>
@@ -3173,10 +3176,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>5</v>
@@ -3184,10 +3187,10 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>5</v>
@@ -3195,10 +3198,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>5</v>
@@ -3209,7 +3212,7 @@
         <v>65</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>5</v>
@@ -3217,10 +3220,10 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>5</v>
@@ -3228,10 +3231,10 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>5</v>
@@ -3242,7 +3245,7 @@
         <v>72</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>5</v>
@@ -3250,10 +3253,10 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>5</v>
@@ -3264,7 +3267,7 @@
         <v>65</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>5</v>
@@ -3272,10 +3275,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>5</v>
@@ -3283,10 +3286,10 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>5</v>
@@ -3294,10 +3297,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>5</v>
@@ -3305,7 +3308,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>105</v>
@@ -3319,7 +3322,7 @@
         <v>72</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>5</v>
@@ -3327,7 +3330,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>107</v>
@@ -3341,7 +3344,7 @@
         <v>108</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>5</v>
@@ -3349,10 +3352,10 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>5</v>
@@ -3363,7 +3366,7 @@
         <v>111</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>5</v>
@@ -3371,10 +3374,10 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>5</v>
@@ -3385,7 +3388,7 @@
         <v>65</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>5</v>
@@ -3393,10 +3396,10 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>5</v>
@@ -3404,10 +3407,10 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>5</v>
@@ -3415,10 +3418,10 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>5</v>
@@ -3426,10 +3429,10 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>5</v>
@@ -3437,10 +3440,10 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>5</v>
@@ -3448,10 +3451,10 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>5</v>
@@ -3462,7 +3465,7 @@
         <v>72</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>5</v>
@@ -3470,7 +3473,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>117</v>
@@ -3484,7 +3487,7 @@
         <v>118</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>5</v>
@@ -3492,10 +3495,10 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>5</v>
@@ -3503,10 +3506,10 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>5</v>
@@ -3517,7 +3520,7 @@
         <v>122</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>5</v>
@@ -3525,7 +3528,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>123</v>
@@ -3536,10 +3539,10 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>5</v>
@@ -3547,7 +3550,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>125</v>
@@ -3594,7 +3597,7 @@
         <v>132</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>5</v>
@@ -3602,10 +3605,10 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>5</v>
@@ -3613,10 +3616,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>5</v>
@@ -3624,10 +3627,10 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>5</v>
@@ -3635,7 +3638,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>138</v>
@@ -3649,7 +3652,7 @@
         <v>139</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>5</v>
@@ -3657,10 +3660,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>5</v>
@@ -3668,10 +3671,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>5</v>
@@ -3679,10 +3682,10 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>5</v>
@@ -3693,7 +3696,7 @@
         <v>144</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>5</v>
@@ -3701,10 +3704,10 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>5</v>
@@ -3715,7 +3718,7 @@
         <v>65</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>5</v>
@@ -3723,10 +3726,10 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>5</v>
@@ -3734,10 +3737,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>5</v>
@@ -3745,10 +3748,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>5</v>
@@ -3756,10 +3759,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>5</v>
@@ -3767,10 +3770,10 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>5</v>
@@ -3778,10 +3781,10 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>147</v>
+        <v>7</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>5</v>
@@ -3792,7 +3795,7 @@
         <v>72</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>5</v>
@@ -3800,10 +3803,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>5</v>
@@ -3811,10 +3814,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>5</v>
@@ -3844,10 +3847,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>5</v>
@@ -3855,7 +3858,7 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>157</v>
@@ -3866,10 +3869,10 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>5</v>
@@ -3877,10 +3880,10 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>5</v>
@@ -3888,10 +3891,10 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>5</v>
@@ -3902,7 +3905,7 @@
         <v>108</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>5</v>
@@ -3910,7 +3913,7 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>162</v>
@@ -3924,7 +3927,7 @@
         <v>163</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>5</v>
@@ -3932,10 +3935,10 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>5</v>
@@ -3943,10 +3946,10 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>5</v>
@@ -3954,10 +3957,10 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>5</v>
@@ -3968,7 +3971,7 @@
         <v>65</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>5</v>
@@ -3976,10 +3979,10 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>5</v>
@@ -3987,10 +3990,10 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>5</v>
@@ -3998,10 +4001,10 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>5</v>
@@ -4009,7 +4012,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>168</v>
@@ -4023,7 +4026,7 @@
         <v>72</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>5</v>
@@ -4031,10 +4034,10 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>5</v>
@@ -4042,10 +4045,10 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>63</v>
+        <v>171</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>5</v>
@@ -4056,7 +4059,7 @@
         <v>65</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>5</v>
@@ -4064,10 +4067,10 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>170</v>
+        <v>67</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>5</v>
@@ -4075,10 +4078,10 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>5</v>
@@ -4086,10 +4089,10 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>5</v>
@@ -4097,10 +4100,10 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>5</v>
@@ -4108,10 +4111,10 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>5</v>
@@ -4119,10 +4122,10 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>5</v>
@@ -4130,10 +4133,10 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>173</v>
+        <v>72</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>5</v>
@@ -4141,10 +4144,10 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>5</v>
@@ -4152,10 +4155,10 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>5</v>
@@ -4199,7 +4202,7 @@
         <v>182</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>5</v>
@@ -4207,10 +4210,10 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>5</v>
@@ -4218,10 +4221,10 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>5</v>
@@ -4229,10 +4232,10 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>5</v>
@@ -4240,10 +4243,10 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>5</v>
@@ -4251,10 +4254,10 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>5</v>
@@ -4309,7 +4312,7 @@
         <v>196</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>7</v>
+        <v>197</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>5</v>
@@ -4317,10 +4320,10 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>63</v>
+        <v>198</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>5</v>
@@ -4331,7 +4334,7 @@
         <v>65</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>5</v>
@@ -4339,10 +4342,10 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>197</v>
+        <v>67</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>5</v>
@@ -4350,10 +4353,10 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>5</v>
@@ -4361,10 +4364,10 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>5</v>
@@ -4372,10 +4375,10 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>5</v>
@@ -4383,10 +4386,10 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>5</v>
@@ -4394,10 +4397,10 @@
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>199</v>
+        <v>71</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>5</v>
@@ -4405,10 +4408,10 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>70</v>
+        <v>201</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>200</v>
+        <v>9</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>5</v>
@@ -4419,7 +4422,7 @@
         <v>72</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>5</v>
@@ -4427,10 +4430,10 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>5</v>
@@ -4438,10 +4441,10 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>5</v>
@@ -4452,7 +4455,7 @@
         <v>204</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>5</v>
@@ -4460,10 +4463,10 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>5</v>
@@ -4471,10 +4474,10 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>5</v>
@@ -4482,10 +4485,10 @@
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>208</v>
+        <v>30</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>5</v>
@@ -4493,10 +4496,10 @@
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>5</v>
@@ -4504,10 +4507,10 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>28</v>
+        <v>211</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>5</v>
@@ -4515,10 +4518,10 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>212</v>
+        <v>30</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>5</v>
@@ -4526,7 +4529,7 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>213</v>
@@ -4537,7 +4540,7 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>215</v>
@@ -4617,7 +4620,7 @@
         <v>228</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>5</v>
@@ -4625,10 +4628,10 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>5</v>
@@ -4661,7 +4664,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>5</v>
@@ -4669,10 +4672,10 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>5</v>
@@ -4680,10 +4683,10 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>5</v>
@@ -4705,7 +4708,7 @@
         <v>241</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>5</v>
@@ -4713,10 +4716,10 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>5</v>
@@ -4724,10 +4727,10 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>5</v>
@@ -4738,7 +4741,7 @@
         <v>245</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>5</v>
@@ -4746,10 +4749,10 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>5</v>
@@ -4771,7 +4774,7 @@
         <v>250</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>5</v>
@@ -4779,10 +4782,10 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B233" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>5</v>
@@ -4790,10 +4793,10 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>5</v>
@@ -4801,10 +4804,10 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>5</v>
@@ -4812,10 +4815,10 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>5</v>
@@ -4823,10 +4826,10 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>5</v>
@@ -4834,10 +4837,10 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>5</v>
@@ -4848,7 +4851,7 @@
         <v>258</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>5</v>
@@ -4856,10 +4859,10 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>257</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>5</v>
@@ -4867,10 +4870,10 @@
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>5</v>
@@ -4878,10 +4881,10 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>5</v>
@@ -4889,10 +4892,10 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>5</v>
@@ -4903,7 +4906,7 @@
         <v>264</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>5</v>
@@ -4911,10 +4914,10 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B245" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>5</v>
@@ -4925,7 +4928,7 @@
         <v>267</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>5</v>
@@ -4933,10 +4936,10 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>5</v>
@@ -4944,10 +4947,10 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>5</v>
@@ -4955,10 +4958,10 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>5</v>
@@ -4980,7 +4983,7 @@
         <v>274</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>5</v>
@@ -4988,10 +4991,10 @@
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>5</v>
@@ -5002,7 +5005,7 @@
         <v>277</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>5</v>
@@ -5010,10 +5013,10 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>5</v>
@@ -5021,10 +5024,10 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>106</v>
+        <v>280</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>5</v>
@@ -5035,7 +5038,7 @@
         <v>108</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>5</v>
@@ -5043,10 +5046,10 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>5</v>
@@ -5054,7 +5057,7 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>282</v>
+        <v>63</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>283</v>
@@ -5120,10 +5123,10 @@
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>5</v>
@@ -5131,10 +5134,10 @@
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>5</v>
@@ -5142,10 +5145,10 @@
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>149</v>
+        <v>294</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>5</v>
@@ -5153,10 +5156,10 @@
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>5</v>
@@ -5167,7 +5170,7 @@
         <v>65</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>5</v>
@@ -5175,10 +5178,10 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>298</v>
+        <v>67</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>5</v>
@@ -5186,10 +5189,10 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>69</v>
+        <v>300</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>5</v>
@@ -5197,7 +5200,7 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>299</v>
@@ -5211,7 +5214,7 @@
         <v>72</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>5</v>
@@ -5219,10 +5222,10 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>5</v>
@@ -5233,7 +5236,7 @@
         <v>65</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>5</v>
@@ -5241,10 +5244,10 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>5</v>
@@ -5252,7 +5255,7 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>301</v>
+        <v>71</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>302</v>
@@ -5263,10 +5266,10 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>70</v>
+        <v>303</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>5</v>
@@ -5277,7 +5280,7 @@
         <v>72</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>5</v>
@@ -5285,10 +5288,10 @@
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>5</v>
@@ -5296,10 +5299,10 @@
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>5</v>
@@ -5307,7 +5310,7 @@
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>305</v>
+        <v>96</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>306</v>
@@ -5351,10 +5354,10 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>180</v>
+        <v>313</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>5</v>
@@ -5365,7 +5368,7 @@
         <v>182</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>5</v>
@@ -5373,10 +5376,10 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>314</v>
+        <v>184</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>5</v>
@@ -5384,10 +5387,10 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B288" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>5</v>
@@ -5395,10 +5398,10 @@
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>5</v>
@@ -5409,7 +5412,7 @@
         <v>318</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>5</v>
@@ -5417,10 +5420,10 @@
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>109</v>
+        <v>320</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>5</v>
@@ -5428,7 +5431,7 @@
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>319</v>
@@ -5439,7 +5442,7 @@
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>320</v>
+        <v>111</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>321</v>
@@ -5453,7 +5456,7 @@
         <v>322</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>321</v>
+        <v>4</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>5</v>
@@ -5464,7 +5467,7 @@
         <v>323</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>321</v>
+        <v>4</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>5</v>
@@ -5475,7 +5478,7 @@
         <v>324</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>321</v>
+        <v>4</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>5</v>
@@ -5486,7 +5489,7 @@
         <v>325</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>321</v>
+        <v>4</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>5</v>
@@ -5497,7 +5500,7 @@
         <v>326</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>327</v>
+        <v>4</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>5</v>
@@ -5505,10 +5508,10 @@
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>5</v>
@@ -5516,10 +5519,10 @@
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B300" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>5</v>
@@ -5530,7 +5533,7 @@
         <v>331</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>5</v>
@@ -5541,7 +5544,7 @@
         <v>332</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>5</v>
@@ -5549,10 +5552,10 @@
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B303" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>5</v>
@@ -5563,7 +5566,7 @@
         <v>335</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>5</v>
@@ -5571,7 +5574,7 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>337</v>
@@ -5582,7 +5585,7 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>338</v>
@@ -5593,7 +5596,7 @@
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B307" s="1" t="s">
         <v>339</v>
@@ -5604,7 +5607,7 @@
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B308" s="1" t="s">
         <v>340</v>
@@ -5615,7 +5618,7 @@
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B309" s="1" t="s">
         <v>341</v>
@@ -5626,7 +5629,7 @@
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B310" s="1" t="s">
         <v>342</v>
@@ -5637,7 +5640,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>149</v>
+        <v>336</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>343</v>
@@ -5648,7 +5651,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>344</v>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>19</v>
+        <v>151</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>345</v>
@@ -5670,7 +5673,7 @@
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>346</v>
@@ -5681,7 +5684,7 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B315" s="1" t="s">
         <v>347</v>
@@ -5692,7 +5695,7 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B316" s="1" t="s">
         <v>348</v>
@@ -5703,10 +5706,10 @@
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>5</v>
@@ -5714,10 +5717,10 @@
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="B318" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>5</v>
@@ -5725,10 +5728,10 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B319" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="B319" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>5</v>
@@ -5736,10 +5739,10 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>35</v>
+        <v>352</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>5</v>
@@ -5747,10 +5750,10 @@
     </row>
     <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>5</v>
@@ -5758,10 +5761,10 @@
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>5</v>
@@ -5769,10 +5772,10 @@
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>5</v>
@@ -5780,10 +5783,10 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="B324" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>5</v>
@@ -5794,7 +5797,7 @@
         <v>354</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>5</v>
@@ -5802,10 +5805,10 @@
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B326" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="B326" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>5</v>
@@ -5816,7 +5819,7 @@
         <v>357</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>5</v>
@@ -5827,7 +5830,7 @@
         <v>358</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>5</v>
@@ -5838,7 +5841,7 @@
         <v>359</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>5</v>
@@ -5849,7 +5852,7 @@
         <v>360</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>5</v>
@@ -5857,10 +5860,10 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>5</v>
@@ -5871,7 +5874,7 @@
         <v>363</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>5</v>
@@ -5879,10 +5882,10 @@
     </row>
     <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="1" t="s">
-        <v>59</v>
+        <v>364</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>5</v>
@@ -5890,10 +5893,10 @@
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B334" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>5</v>
@@ -5901,10 +5904,10 @@
     </row>
     <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="1" t="s">
-        <v>63</v>
+        <v>366</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>5</v>
@@ -5915,7 +5918,7 @@
         <v>65</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>5</v>
@@ -5923,10 +5926,10 @@
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="s">
-        <v>366</v>
+        <v>67</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>5</v>
@@ -5937,7 +5940,7 @@
         <v>367</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>5</v>
@@ -5945,10 +5948,10 @@
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="s">
-        <v>68</v>
+        <v>368</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>5</v>
@@ -5956,10 +5959,10 @@
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>5</v>
@@ -5967,10 +5970,10 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>5</v>
@@ -5978,10 +5981,10 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>368</v>
+        <v>10</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>5</v>
@@ -5992,7 +5995,7 @@
         <v>72</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>5</v>
@@ -6000,10 +6003,10 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="B344" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>5</v>
@@ -6011,10 +6014,10 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="s">
-        <v>188</v>
+        <v>370</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>5</v>
@@ -6022,10 +6025,10 @@
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="B346" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>5</v>
@@ -6036,7 +6039,7 @@
         <v>372</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>5</v>
@@ -6047,7 +6050,7 @@
         <v>373</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>5</v>
@@ -6058,7 +6061,7 @@
         <v>374</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>5</v>
@@ -6069,7 +6072,7 @@
         <v>375</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>5</v>
@@ -6077,10 +6080,10 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B351" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>5</v>
@@ -6088,7 +6091,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>379</v>
@@ -6099,10 +6102,10 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B353" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>5</v>
@@ -6110,10 +6113,10 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="B354" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>5</v>
@@ -6121,10 +6124,10 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>5</v>
@@ -6132,10 +6135,10 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>5</v>
@@ -6146,7 +6149,7 @@
         <v>387</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>5</v>
@@ -6154,10 +6157,10 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B358" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B358" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>5</v>
@@ -6168,7 +6171,7 @@
         <v>390</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>5</v>
@@ -6176,7 +6179,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="s">
-        <v>28</v>
+        <v>391</v>
       </c>
       <c r="B360" s="1" t="s">
         <v>392</v>
@@ -6187,10 +6190,10 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>5</v>
@@ -6198,10 +6201,10 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B362" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B362" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>5</v>
@@ -6209,10 +6212,10 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="s">
-        <v>63</v>
+        <v>394</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>5</v>
@@ -6223,7 +6226,7 @@
         <v>65</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>5</v>
@@ -6231,10 +6234,10 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>5</v>
@@ -6242,10 +6245,10 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>5</v>
@@ -6253,10 +6256,10 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B367" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B367" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>5</v>
@@ -6264,10 +6267,10 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="s">
-        <v>68</v>
+        <v>396</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>5</v>
@@ -6289,7 +6292,7 @@
         <v>72</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>5</v>
@@ -6297,7 +6300,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>398</v>
@@ -6308,10 +6311,10 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>5</v>
@@ -6319,10 +6322,10 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B373" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B373" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>5</v>
@@ -6330,10 +6333,10 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="s">
-        <v>116</v>
+        <v>400</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>5</v>
@@ -6344,7 +6347,7 @@
         <v>118</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>5</v>
@@ -6352,10 +6355,10 @@
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>5</v>
@@ -6363,10 +6366,10 @@
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="s">
-        <v>119</v>
+        <v>401</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>5</v>
@@ -6374,10 +6377,10 @@
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>401</v>
+        <v>11</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>5</v>
@@ -6388,7 +6391,7 @@
         <v>122</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>5</v>
@@ -6396,10 +6399,10 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B380" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B380" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>5</v>
@@ -6407,10 +6410,10 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="s">
-        <v>63</v>
+        <v>403</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>5</v>
@@ -6421,7 +6424,7 @@
         <v>65</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>5</v>
@@ -6429,10 +6432,10 @@
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B383" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B383" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>5</v>
@@ -6440,10 +6443,10 @@
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="s">
-        <v>68</v>
+        <v>405</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>5</v>
@@ -6451,10 +6454,10 @@
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>5</v>
@@ -6462,10 +6465,10 @@
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>5</v>
@@ -6473,10 +6476,10 @@
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>5</v>
@@ -6487,7 +6490,7 @@
         <v>72</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>5</v>
@@ -6495,10 +6498,10 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B389" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B389" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>5</v>
@@ -6506,7 +6509,7 @@
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="s">
-        <v>19</v>
+        <v>407</v>
       </c>
       <c r="B390" s="1" t="s">
         <v>408</v>
@@ -6517,10 +6520,10 @@
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B391" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B391" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>5</v>
@@ -6531,7 +6534,7 @@
         <v>410</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>5</v>
@@ -6539,10 +6542,10 @@
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="s">
-        <v>63</v>
+        <v>411</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>5</v>
@@ -6550,10 +6553,10 @@
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="s">
-        <v>411</v>
+        <v>65</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>412</v>
+        <v>12</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>5</v>
@@ -6561,10 +6564,10 @@
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="s">
-        <v>70</v>
+        <v>412</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>5</v>
@@ -6572,7 +6575,7 @@
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B396" s="1" t="s">
         <v>413</v>
@@ -6583,7 +6586,7 @@
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="B397" s="1" t="s">
         <v>414</v>
@@ -6594,10 +6597,10 @@
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="s">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>5</v>
@@ -6605,10 +6608,10 @@
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B399" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B399" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>5</v>
@@ -6616,10 +6619,10 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="s">
-        <v>63</v>
+        <v>416</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>5</v>
@@ -6630,7 +6633,7 @@
         <v>65</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>5</v>
@@ -6638,10 +6641,10 @@
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B402" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="B402" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>5</v>
@@ -6649,10 +6652,10 @@
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="s">
-        <v>68</v>
+        <v>418</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>5</v>
@@ -6660,10 +6663,10 @@
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>5</v>
@@ -6671,10 +6674,10 @@
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>5</v>
@@ -6685,7 +6688,7 @@
         <v>72</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>5</v>
@@ -6693,7 +6696,7 @@
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="s">
-        <v>419</v>
+        <v>74</v>
       </c>
       <c r="B407" s="1" t="s">
         <v>419</v>
@@ -6707,7 +6710,7 @@
         <v>420</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>5</v>
@@ -6715,10 +6718,10 @@
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="s">
-        <v>63</v>
+        <v>421</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>5</v>
@@ -6729,7 +6732,7 @@
         <v>65</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>5</v>
@@ -6737,10 +6740,10 @@
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>5</v>
@@ -6748,10 +6751,10 @@
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B412" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="B412" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>5</v>
@@ -6762,7 +6765,7 @@
         <v>423</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>5</v>
@@ -6770,10 +6773,10 @@
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="s">
-        <v>69</v>
+        <v>424</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>5</v>
@@ -6781,10 +6784,10 @@
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>5</v>
@@ -6795,7 +6798,7 @@
         <v>72</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>5</v>
@@ -6803,10 +6806,10 @@
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B417" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="B417" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>5</v>
@@ -6817,7 +6820,7 @@
         <v>426</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>5</v>
@@ -6825,10 +6828,10 @@
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B419" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="B419" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>5</v>
@@ -6839,7 +6842,7 @@
         <v>429</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>5</v>
@@ -6847,10 +6850,10 @@
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="s">
-        <v>109</v>
+        <v>430</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>5</v>
@@ -6858,10 +6861,10 @@
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="s">
-        <v>430</v>
+        <v>111</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>5</v>
@@ -6869,10 +6872,10 @@
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B423" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="B423" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>5</v>
@@ -6883,7 +6886,7 @@
         <v>433</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>5</v>
@@ -6891,10 +6894,10 @@
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="s">
-        <v>109</v>
+        <v>434</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>5</v>
@@ -6902,10 +6905,10 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>5</v>
@@ -6913,10 +6916,10 @@
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B427" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="B427" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>5</v>
@@ -6924,10 +6927,10 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B428" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="B428" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>5</v>
@@ -6938,7 +6941,7 @@
         <v>438</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>5</v>
@@ -6949,7 +6952,7 @@
         <v>439</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>5</v>
@@ -6960,7 +6963,7 @@
         <v>440</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>5</v>
@@ -6968,10 +6971,10 @@
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B432" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="B432" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>5</v>
@@ -6979,10 +6982,10 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B433" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="B433" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>5</v>
@@ -6990,10 +6993,10 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B434" s="1" t="s">
         <v>446</v>
-      </c>
-      <c r="B434" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>5</v>
@@ -7004,7 +7007,7 @@
         <v>447</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>5</v>
@@ -7015,7 +7018,7 @@
         <v>448</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>5</v>
@@ -7023,10 +7026,10 @@
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B437" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="B437" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>5</v>
@@ -7037,7 +7040,7 @@
         <v>451</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>5</v>
@@ -7048,7 +7051,7 @@
         <v>452</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>5</v>
@@ -7059,7 +7062,7 @@
         <v>453</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>5</v>
@@ -7067,10 +7070,10 @@
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B441" s="1" t="s">
         <v>455</v>
-      </c>
-      <c r="B441" s="1" t="s">
-        <v>456</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>5</v>
@@ -7078,7 +7081,7 @@
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="s">
-        <v>19</v>
+        <v>456</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>457</v>
@@ -7089,10 +7092,10 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B443" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="B443" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>5</v>
@@ -7100,10 +7103,10 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B444" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="B444" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>5</v>
@@ -7114,7 +7117,7 @@
         <v>461</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>5</v>
@@ -7122,10 +7125,10 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B446" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="B446" s="1" t="s">
-        <v>462</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>5</v>
@@ -7136,7 +7139,7 @@
         <v>464</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>5</v>
@@ -7144,7 +7147,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="s">
-        <v>93</v>
+        <v>465</v>
       </c>
       <c r="B448" s="1" t="s">
         <v>466</v>
@@ -7155,10 +7158,10 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>5</v>
@@ -7166,7 +7169,7 @@
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="B450" s="1" t="s">
         <v>467</v>
@@ -7188,10 +7191,10 @@
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B452" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="B452" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>5</v>
@@ -7199,10 +7202,10 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="B453" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="B453" s="1" t="s">
-        <v>470</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>5</v>
@@ -7210,10 +7213,10 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>5</v>
@@ -7221,10 +7224,10 @@
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>5</v>
@@ -7232,10 +7235,10 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B456" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="B456" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>5</v>
@@ -7243,10 +7246,10 @@
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B457" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="B457" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>5</v>
@@ -7257,7 +7260,7 @@
         <v>476</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>5</v>
@@ -7268,7 +7271,7 @@
         <v>477</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>5</v>
@@ -7276,10 +7279,10 @@
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="s">
-        <v>59</v>
+        <v>478</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>5</v>
@@ -7287,10 +7290,10 @@
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>5</v>
@@ -7298,7 +7301,7 @@
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>479</v>
@@ -7309,7 +7312,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>480</v>
@@ -7323,7 +7326,7 @@
         <v>176</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>5</v>
@@ -7334,7 +7337,7 @@
         <v>178</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>5</v>
@@ -7342,10 +7345,10 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B466" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="B466" s="1" t="s">
-        <v>482</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>5</v>
@@ -7353,10 +7356,10 @@
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B467" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="B467" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>5</v>
@@ -7364,7 +7367,7 @@
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B468" s="1" t="s">
         <v>485</v>
@@ -7375,7 +7378,7 @@
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="s">
-        <v>19</v>
+        <v>484</v>
       </c>
       <c r="B469" s="1" t="s">
         <v>486</v>
@@ -7386,7 +7389,7 @@
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="B470" s="1" t="s">
         <v>487</v>
@@ -7400,7 +7403,7 @@
         <v>65</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>5</v>
@@ -7408,10 +7411,10 @@
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B472" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="B472" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>5</v>
@@ -7419,10 +7422,10 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="s">
-        <v>68</v>
+        <v>489</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>5</v>
@@ -7430,10 +7433,10 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>5</v>
@@ -7441,10 +7444,10 @@
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>5</v>
@@ -7455,7 +7458,7 @@
         <v>72</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>5</v>
@@ -7463,10 +7466,10 @@
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B477" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="B477" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>5</v>
@@ -7474,10 +7477,10 @@
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="s">
-        <v>63</v>
+        <v>491</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>5</v>
@@ -7488,7 +7491,7 @@
         <v>65</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>5</v>
@@ -7496,10 +7499,10 @@
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>5</v>
@@ -7507,10 +7510,10 @@
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>5</v>
@@ -7518,10 +7521,10 @@
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="s">
-        <v>491</v>
+        <v>116</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>5</v>
@@ -7532,7 +7535,7 @@
         <v>492</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>5</v>
@@ -7540,10 +7543,10 @@
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="s">
-        <v>69</v>
+        <v>493</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>5</v>
@@ -7551,10 +7554,10 @@
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>493</v>
+        <v>13</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>5</v>
@@ -7565,7 +7568,7 @@
         <v>72</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>5</v>
@@ -7573,10 +7576,10 @@
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B487" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="B487" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>5</v>
@@ -7587,7 +7590,7 @@
         <v>495</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>5</v>
@@ -7598,7 +7601,7 @@
         <v>496</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>5</v>
@@ -7606,10 +7609,10 @@
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B490" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="B490" s="1" t="s">
-        <v>497</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>5</v>
@@ -7617,10 +7620,10 @@
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="s">
-        <v>116</v>
+        <v>499</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>5</v>
@@ -7631,7 +7634,7 @@
         <v>118</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>5</v>
@@ -7639,10 +7642,10 @@
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>5</v>
@@ -7650,7 +7653,7 @@
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>500</v>
@@ -7664,7 +7667,7 @@
         <v>122</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>5</v>
@@ -7672,10 +7675,10 @@
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B496" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="B496" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>5</v>
@@ -7683,10 +7686,10 @@
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B497" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="B497" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>5</v>
@@ -7694,10 +7697,10 @@
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B498" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="B498" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>5</v>
@@ -7705,10 +7708,10 @@
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B499" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="B499" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>5</v>
@@ -7716,10 +7719,10 @@
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B500" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="B500" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>5</v>
@@ -7727,10 +7730,10 @@
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B501" s="1" t="s">
         <v>511</v>
-      </c>
-      <c r="B501" s="1" t="s">
-        <v>510</v>
       </c>
       <c r="C501" s="1" t="s">
         <v>5</v>
@@ -7741,7 +7744,7 @@
         <v>512</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C502" s="1" t="s">
         <v>5</v>
@@ -7749,10 +7752,10 @@
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B503" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="B503" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="C503" s="1" t="s">
         <v>5</v>
@@ -7760,10 +7763,10 @@
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B504" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="B504" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="C504" s="1" t="s">
         <v>5</v>
@@ -7771,10 +7774,10 @@
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B505" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="B505" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="C505" s="1" t="s">
         <v>5</v>
@@ -7782,7 +7785,7 @@
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B506" s="1" t="s">
         <v>520</v>
@@ -7796,7 +7799,7 @@
         <v>521</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C507" s="1" t="s">
         <v>5</v>
@@ -7807,7 +7810,7 @@
         <v>522</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>12</v>
+        <v>521</v>
       </c>
       <c r="C508" s="1" t="s">
         <v>5</v>
@@ -7818,7 +7821,7 @@
         <v>523</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C509" s="1" t="s">
         <v>5</v>
@@ -7826,10 +7829,10 @@
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="s">
-        <v>63</v>
+        <v>524</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C510" s="1" t="s">
         <v>5</v>
@@ -7837,10 +7840,10 @@
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="s">
-        <v>524</v>
+        <v>65</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>525</v>
+        <v>14</v>
       </c>
       <c r="C511" s="1" t="s">
         <v>5</v>
@@ -7848,10 +7851,10 @@
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="s">
-        <v>70</v>
+        <v>525</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C512" s="1" t="s">
         <v>5</v>
@@ -7859,7 +7862,7 @@
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B513" s="1" t="s">
         <v>526</v>
@@ -7873,7 +7876,7 @@
         <v>65</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C514" s="1" t="s">
         <v>5</v>
@@ -7881,10 +7884,10 @@
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B515" s="1" t="s">
         <v>527</v>
-      </c>
-      <c r="B515" s="1" t="s">
-        <v>526</v>
       </c>
       <c r="C515" s="1" t="s">
         <v>5</v>
@@ -7895,7 +7898,7 @@
         <v>528</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C516" s="1" t="s">
         <v>5</v>
@@ -7903,10 +7906,10 @@
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>69</v>
+        <v>529</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C517" s="1" t="s">
         <v>5</v>
@@ -7914,10 +7917,10 @@
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="s">
-        <v>529</v>
+        <v>71</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C518" s="1" t="s">
         <v>5</v>
@@ -7925,7 +7928,7 @@
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="s">
-        <v>70</v>
+        <v>530</v>
       </c>
       <c r="B519" s="1" t="s">
         <v>531</v>
@@ -7939,7 +7942,7 @@
         <v>72</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C520" s="1" t="s">
         <v>5</v>
@@ -7947,10 +7950,10 @@
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B521" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="B521" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="C521" s="1" t="s">
         <v>5</v>
@@ -7958,7 +7961,7 @@
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="s">
-        <v>63</v>
+        <v>533</v>
       </c>
       <c r="B522" s="1" t="s">
         <v>534</v>
@@ -7972,7 +7975,7 @@
         <v>65</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C523" s="1" t="s">
         <v>5</v>
@@ -7980,10 +7983,10 @@
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B524" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="B524" s="1" t="s">
-        <v>534</v>
       </c>
       <c r="C524" s="1" t="s">
         <v>5</v>
@@ -7994,7 +7997,7 @@
         <v>536</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C525" s="1" t="s">
         <v>5</v>
@@ -8002,10 +8005,10 @@
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="s">
-        <v>69</v>
+        <v>537</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C526" s="1" t="s">
         <v>5</v>
@@ -8013,10 +8016,10 @@
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="s">
-        <v>537</v>
+        <v>71</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C527" s="1" t="s">
         <v>5</v>
@@ -8024,10 +8027,10 @@
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="s">
-        <v>70</v>
+        <v>538</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C528" s="1" t="s">
         <v>5</v>
@@ -8038,7 +8041,7 @@
         <v>72</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C529" s="1" t="s">
         <v>5</v>
@@ -8046,7 +8049,7 @@
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>539</v>
@@ -8060,7 +8063,7 @@
         <v>118</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C531" s="1" t="s">
         <v>5</v>
@@ -8068,10 +8071,10 @@
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C532" s="1" t="s">
         <v>5</v>
@@ -8079,7 +8082,7 @@
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B533" s="1" t="s">
         <v>540</v>
@@ -8093,7 +8096,7 @@
         <v>122</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C534" s="1" t="s">
         <v>5</v>
@@ -8101,7 +8104,7 @@
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="s">
-        <v>501</v>
+        <v>124</v>
       </c>
       <c r="B535" s="1" t="s">
         <v>541</v>
@@ -8112,10 +8115,10 @@
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B536" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="B536" s="1" t="s">
-        <v>543</v>
       </c>
       <c r="C536" s="1" t="s">
         <v>5</v>
@@ -8123,10 +8126,10 @@
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B537" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="B537" s="1" t="s">
-        <v>545</v>
       </c>
       <c r="C537" s="1" t="s">
         <v>5</v>
@@ -8134,10 +8137,10 @@
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B538" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="B538" s="1" t="s">
-        <v>545</v>
       </c>
       <c r="C538" s="1" t="s">
         <v>5</v>
@@ -8148,7 +8151,7 @@
         <v>547</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C539" s="1" t="s">
         <v>5</v>
@@ -8156,10 +8159,10 @@
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C540" s="1" t="s">
         <v>5</v>
@@ -8167,10 +8170,10 @@
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B541" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="B541" s="1" t="s">
-        <v>548</v>
       </c>
       <c r="C541" s="1" t="s">
         <v>5</v>
@@ -8178,10 +8181,10 @@
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C542" s="1" t="s">
         <v>5</v>
@@ -8189,10 +8192,10 @@
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C543" s="1" t="s">
         <v>5</v>
@@ -8200,10 +8203,10 @@
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C544" s="1" t="s">
         <v>5</v>
@@ -8211,7 +8214,7 @@
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="s">
-        <v>372</v>
+        <v>547</v>
       </c>
       <c r="B545" s="1" t="s">
         <v>551</v>
@@ -8222,10 +8225,10 @@
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B546" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="B546" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="C546" s="1" t="s">
         <v>5</v>
@@ -8233,10 +8236,10 @@
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B547" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="B547" s="1" t="s">
-        <v>555</v>
       </c>
       <c r="C547" s="1" t="s">
         <v>5</v>
@@ -8244,10 +8247,10 @@
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B548" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="B548" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="C548" s="1" t="s">
         <v>5</v>
@@ -8255,10 +8258,10 @@
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C549" s="1" t="s">
         <v>5</v>
@@ -8266,10 +8269,10 @@
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B550" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="B550" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="C550" s="1" t="s">
         <v>5</v>
@@ -8277,10 +8280,10 @@
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B551" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="B551" s="1" t="s">
-        <v>561</v>
       </c>
       <c r="C551" s="1" t="s">
         <v>5</v>
@@ -8288,7 +8291,7 @@
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>562</v>
@@ -8299,7 +8302,7 @@
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="s">
-        <v>371</v>
+        <v>555</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>563</v>
@@ -8313,7 +8316,7 @@
         <v>372</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C554" s="1" t="s">
         <v>5</v>
@@ -8324,7 +8327,7 @@
         <v>373</v>
       </c>
       <c r="B555" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C555" s="1" t="s">
         <v>5</v>
@@ -8332,10 +8335,10 @@
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B556" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="B556" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="C556" s="1" t="s">
         <v>5</v>
@@ -8346,7 +8349,7 @@
         <v>565</v>
       </c>
       <c r="B557" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C557" s="1" t="s">
         <v>5</v>
@@ -8357,7 +8360,7 @@
         <v>566</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C558" s="1" t="s">
         <v>5</v>
@@ -8368,7 +8371,7 @@
         <v>567</v>
       </c>
       <c r="B559" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C559" s="1" t="s">
         <v>5</v>
@@ -8379,7 +8382,7 @@
         <v>568</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C560" s="1" t="s">
         <v>5</v>
@@ -8390,7 +8393,7 @@
         <v>569</v>
       </c>
       <c r="B561" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C561" s="1" t="s">
         <v>5</v>
@@ -8401,7 +8404,7 @@
         <v>570</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C562" s="1" t="s">
         <v>5</v>
@@ -8412,7 +8415,7 @@
         <v>571</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C563" s="1" t="s">
         <v>5</v>
@@ -8420,10 +8423,10 @@
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="s">
-        <v>469</v>
+        <v>572</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C564" s="1" t="s">
         <v>5</v>
@@ -8431,10 +8434,10 @@
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C565" s="1" t="s">
         <v>5</v>
@@ -8442,10 +8445,10 @@
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="s">
-        <v>565</v>
+        <v>472</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="C566" s="1" t="s">
         <v>5</v>
@@ -8456,7 +8459,7 @@
         <v>566</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C567" s="1" t="s">
         <v>5</v>
@@ -8467,7 +8470,7 @@
         <v>567</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C568" s="1" t="s">
         <v>5</v>
@@ -8478,7 +8481,7 @@
         <v>568</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C569" s="1" t="s">
         <v>5</v>
@@ -8489,7 +8492,7 @@
         <v>569</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C570" s="1" t="s">
         <v>5</v>
@@ -8500,7 +8503,7 @@
         <v>570</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C571" s="1" t="s">
         <v>5</v>
@@ -8511,7 +8514,7 @@
         <v>571</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C572" s="1" t="s">
         <v>5</v>
@@ -8519,7 +8522,7 @@
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="B573" s="1" t="s">
         <v>573</v>
@@ -8533,7 +8536,7 @@
         <v>566</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C574" s="1" t="s">
         <v>5</v>
@@ -8544,7 +8547,7 @@
         <v>567</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C575" s="1" t="s">
         <v>5</v>
@@ -8555,7 +8558,7 @@
         <v>568</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C576" s="1" t="s">
         <v>5</v>
@@ -8566,7 +8569,7 @@
         <v>569</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C577" s="1" t="s">
         <v>5</v>
@@ -8577,7 +8580,7 @@
         <v>570</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C578" s="1" t="s">
         <v>5</v>
@@ -8588,7 +8591,7 @@
         <v>571</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C579" s="1" t="s">
         <v>5</v>
@@ -8596,7 +8599,7 @@
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="s">
-        <v>372</v>
+        <v>572</v>
       </c>
       <c r="B580" s="1" t="s">
         <v>574</v>
@@ -8607,10 +8610,10 @@
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B581" s="1" t="s">
         <v>575</v>
-      </c>
-      <c r="B581" s="1" t="s">
-        <v>576</v>
       </c>
       <c r="C581" s="1" t="s">
         <v>5</v>
@@ -8618,10 +8621,10 @@
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B582" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="B582" s="1" t="s">
-        <v>578</v>
       </c>
       <c r="C582" s="1" t="s">
         <v>5</v>
@@ -8629,10 +8632,10 @@
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B583" s="1" t="s">
         <v>579</v>
-      </c>
-      <c r="B583" s="1" t="s">
-        <v>580</v>
       </c>
       <c r="C583" s="1" t="s">
         <v>5</v>
@@ -8640,7 +8643,7 @@
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B584" s="1" t="s">
         <v>581</v>
@@ -8651,10 +8654,10 @@
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B585" s="1" t="s">
         <v>582</v>
-      </c>
-      <c r="B585" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="C585" s="1" t="s">
         <v>5</v>
@@ -8665,7 +8668,7 @@
         <v>583</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C586" s="1" t="s">
         <v>5</v>
@@ -8673,10 +8676,10 @@
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="s">
-        <v>161</v>
+        <v>584</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C587" s="1" t="s">
         <v>5</v>
@@ -8684,10 +8687,10 @@
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="s">
-        <v>584</v>
+        <v>163</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C588" s="1" t="s">
         <v>5</v>
@@ -8695,10 +8698,10 @@
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="B589" s="1" t="s">
         <v>586</v>
-      </c>
-      <c r="B589" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="C589" s="1" t="s">
         <v>5</v>
@@ -8709,7 +8712,7 @@
         <v>587</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C590" s="1" t="s">
         <v>5</v>
@@ -8720,7 +8723,7 @@
         <v>588</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C591" s="1" t="s">
         <v>5</v>
@@ -8731,7 +8734,7 @@
         <v>589</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C592" s="1" t="s">
         <v>5</v>
@@ -8739,10 +8742,10 @@
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B593" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="B593" s="1" t="s">
-        <v>592</v>
       </c>
       <c r="C593" s="1" t="s">
         <v>5</v>
@@ -8750,7 +8753,7 @@
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="s">
-        <v>387</v>
+        <v>592</v>
       </c>
       <c r="B594" s="1" t="s">
         <v>593</v>
@@ -8761,10 +8764,10 @@
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C595" s="1" t="s">
         <v>5</v>
@@ -8783,7 +8786,7 @@
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="s">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="B597" s="1" t="s">
         <v>595</v>
@@ -8794,10 +8797,10 @@
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C598" s="1" t="s">
         <v>5</v>
@@ -8805,10 +8808,10 @@
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="s">
-        <v>59</v>
+        <v>476</v>
       </c>
       <c r="B599" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C599" s="1" t="s">
         <v>5</v>
@@ -8816,7 +8819,7 @@
     </row>
     <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="B600" s="1" t="s">
         <v>596</v>
@@ -8827,7 +8830,7 @@
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B601" s="1" t="s">
         <v>597</v>
@@ -8838,10 +8841,10 @@
     </row>
     <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B602" s="1" t="s">
         <v>598</v>
-      </c>
-      <c r="B602" s="1" t="s">
-        <v>599</v>
       </c>
       <c r="C602" s="1" t="s">
         <v>5</v>
@@ -8849,7 +8852,7 @@
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="s">
-        <v>483</v>
+        <v>599</v>
       </c>
       <c r="B603" s="1" t="s">
         <v>600</v>
@@ -8860,10 +8863,10 @@
     </row>
     <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B604" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="B604" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="C604" s="1" t="s">
         <v>5</v>
@@ -8871,7 +8874,7 @@
     </row>
     <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="s">
-        <v>106</v>
+        <v>602</v>
       </c>
       <c r="B605" s="1" t="s">
         <v>603</v>
@@ -8885,7 +8888,7 @@
         <v>108</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C606" s="1" t="s">
         <v>5</v>
@@ -8893,7 +8896,7 @@
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="B607" s="1" t="s">
         <v>604</v>
@@ -8904,7 +8907,7 @@
     </row>
     <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="s">
-        <v>387</v>
+        <v>18</v>
       </c>
       <c r="B608" s="1" t="s">
         <v>605</v>
@@ -8915,10 +8918,10 @@
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B609" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C609" s="1" t="s">
         <v>5</v>
@@ -8937,7 +8940,7 @@
     </row>
     <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="s">
-        <v>93</v>
+        <v>391</v>
       </c>
       <c r="B611" s="1" t="s">
         <v>607</v>
@@ -8948,10 +8951,10 @@
     </row>
     <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C612" s="1" t="s">
         <v>5</v>
@@ -8959,10 +8962,10 @@
     </row>
     <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B613" s="1" t="s">
         <v>608</v>
-      </c>
-      <c r="B613" s="1" t="s">
-        <v>609</v>
       </c>
       <c r="C613" s="1" t="s">
         <v>5</v>
@@ -8970,7 +8973,7 @@
     </row>
     <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="s">
-        <v>149</v>
+        <v>609</v>
       </c>
       <c r="B614" s="1" t="s">
         <v>610</v>
@@ -8981,10 +8984,10 @@
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B615" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="B615" s="1" t="s">
-        <v>612</v>
       </c>
       <c r="C615" s="1" t="s">
         <v>5</v>
@@ -8992,7 +8995,7 @@
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>106</v>
+        <v>612</v>
       </c>
       <c r="B616" s="1" t="s">
         <v>613</v>
@@ -9006,7 +9009,7 @@
         <v>108</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C617" s="1" t="s">
         <v>5</v>
@@ -9014,7 +9017,7 @@
     </row>
     <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="B618" s="1" t="s">
         <v>614</v>
@@ -9025,7 +9028,7 @@
     </row>
     <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="B619" s="1" t="s">
         <v>615</v>
@@ -9039,7 +9042,7 @@
         <v>108</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C620" s="1" t="s">
         <v>5</v>
@@ -9047,10 +9050,10 @@
     </row>
     <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B621" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="B621" s="1" t="s">
-        <v>617</v>
       </c>
       <c r="C621" s="1" t="s">
         <v>5</v>
@@ -9058,10 +9061,10 @@
     </row>
     <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B622" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="B622" s="1" t="s">
-        <v>617</v>
       </c>
       <c r="C622" s="1" t="s">
         <v>5</v>
@@ -9072,7 +9075,7 @@
         <v>619</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C623" s="1" t="s">
         <v>5</v>
@@ -9080,10 +9083,10 @@
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B624" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="B624" s="1" t="s">
-        <v>620</v>
       </c>
       <c r="C624" s="1" t="s">
         <v>5</v>
@@ -9091,10 +9094,10 @@
     </row>
     <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="s">
-        <v>387</v>
+        <v>622</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C625" s="1" t="s">
         <v>5</v>
@@ -9102,10 +9105,10 @@
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C626" s="1" t="s">
         <v>5</v>
@@ -9124,7 +9127,7 @@
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="s">
-        <v>63</v>
+        <v>391</v>
       </c>
       <c r="B628" s="1" t="s">
         <v>624</v>
@@ -9138,7 +9141,7 @@
         <v>65</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C629" s="1" t="s">
         <v>5</v>
@@ -9146,10 +9149,10 @@
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C630" s="1" t="s">
         <v>5</v>
@@ -9157,10 +9160,10 @@
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C631" s="1" t="s">
         <v>5</v>
@@ -9168,10 +9171,10 @@
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B632" s="1" t="s">
         <v>625</v>
-      </c>
-      <c r="B632" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="C632" s="1" t="s">
         <v>5</v>
@@ -9179,10 +9182,10 @@
     </row>
     <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="s">
-        <v>70</v>
+        <v>626</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C633" s="1" t="s">
         <v>5</v>
@@ -9193,7 +9196,7 @@
         <v>72</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C634" s="1" t="s">
         <v>5</v>
@@ -9201,10 +9204,10 @@
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B635" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="B635" s="1" t="s">
-        <v>628</v>
       </c>
       <c r="C635" s="1" t="s">
         <v>5</v>
@@ -9212,10 +9215,10 @@
     </row>
     <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B636" s="1" t="s">
         <v>629</v>
-      </c>
-      <c r="B636" s="1" t="s">
-        <v>628</v>
       </c>
       <c r="C636" s="1" t="s">
         <v>5</v>
@@ -9226,16 +9229,27 @@
         <v>630</v>
       </c>
       <c r="B637" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A638" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="C637" s="1" t="s">
+      <c r="B638" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C638" s="1" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C637">
-    <sortState ref="A2:C637">
-      <sortCondition ref="A2:A637" customList=""/>
+  <autoFilter ref="A1:C638">
+    <sortState ref="A2:C638">
+      <sortCondition ref="A2:A638" customList=""/>
     </sortState>
   </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
